--- a/ToxCast_model/experiments/prediction/KGML/results/2025-07-28_15-04-25/KGML4Gapfilling_prediction_prediction.xlsx
+++ b/ToxCast_model/experiments/prediction/KGML/results/2025-07-28_15-04-25/KGML4Gapfilling_prediction_prediction.xlsx
@@ -1071,7 +1071,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,13 +1081,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1145,7 +1139,7 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1519,7 +1513,7 @@
     <col min="58" max="58" style="6" width="13.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1695,7 +1689,7 @@
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>58</v>
       </c>
@@ -1871,7 +1865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>60</v>
       </c>
@@ -2047,7 +2041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -2223,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>64</v>
       </c>
@@ -2399,7 +2393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>66</v>
       </c>
@@ -2575,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
@@ -2751,7 +2745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>70</v>
       </c>
@@ -2927,7 +2921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>72</v>
       </c>
@@ -3103,7 +3097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>74</v>
       </c>
@@ -3279,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>76</v>
       </c>
@@ -3455,7 +3449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>78</v>
       </c>
@@ -3631,7 +3625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>80</v>
       </c>
@@ -3807,7 +3801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>82</v>
       </c>
